--- a/load_profile.xlsx
+++ b/load_profile.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t xml:space="preserve">Total RPM</t>
   </si>
@@ -34,36 +34,59 @@
     <t xml:space="preserve">comment</t>
   </si>
   <si>
-    <t xml:space="preserve">100 “average” users as per task</t>
-  </si>
-  <si>
     <t xml:space="preserve">UC</t>
   </si>
   <si>
-    <t xml:space="preserve">TPH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creates or updates 10 issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opens other issues for reading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performs searches</t>
+    <t xml:space="preserve">Desired TPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacing, s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated RPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated TPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UC01_createOrUpdate.scala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UC02_performSearches.scala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -144,20 +167,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -284,80 +315,149 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:I9"/>
+  <dimension ref="A2:M9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="59.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="59.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="32.83"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1"/>
-      <c r="C3" s="2" t="n">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="0" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <f aca="false">(C7*D7/60)*F7</f>
+        <v>32.6666666666667</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <f aca="false">G7*60</f>
+        <v>1960</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="1"/>
+      <c r="E8" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <f aca="false">(C7*D7/60)*F8</f>
+        <v>14</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <f aca="false">G8*60</f>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="0" t="n">
+      <c r="C9" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <f aca="false">C9*D9/60</f>
+        <v>16.6666666666667</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <f aca="false">G9*60</f>
         <v>1000</v>
       </c>
     </row>

--- a/load_profile.xlsx
+++ b/load_profile.xlsx
@@ -20,19 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
-  <si>
-    <t xml:space="preserve">Total RPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coefficient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Result RPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comment</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t xml:space="preserve">UC</t>
   </si>
@@ -46,7 +34,7 @@
     <t xml:space="preserve">Pacing, s</t>
   </si>
   <si>
-    <t xml:space="preserve">action</t>
+    <t xml:space="preserve">Action</t>
   </si>
   <si>
     <t xml:space="preserve">Ratio</t>
@@ -58,7 +46,7 @@
     <t xml:space="preserve">Calculated TPH</t>
   </si>
   <si>
-    <t xml:space="preserve">UC01_createOrUpdate.scala</t>
+    <t xml:space="preserve">UC01_createOrUpdate</t>
   </si>
   <si>
     <t xml:space="preserve">Create</t>
@@ -67,10 +55,13 @@
     <t xml:space="preserve">Update</t>
   </si>
   <si>
-    <t xml:space="preserve">UC02_performSearches.scala</t>
+    <t xml:space="preserve">UC02_performSearches</t>
   </si>
   <si>
     <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UC03_viewIssue</t>
   </si>
 </sst>
 </file>
@@ -315,67 +306,48 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="59.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="32.83"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I1" s="0"/>
+    </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="I2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
+      <c r="I3" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -385,30 +357,30 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>700</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <f aca="false">(C7*D7/60)*F7</f>
-        <v>32.6666666666667</v>
-      </c>
-      <c r="H7" s="3" t="n">
+        <f aca="false">(C7*60/D7)*F7</f>
+        <v>6.35294117647059</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <f aca="false">G7*60</f>
-        <v>1960</v>
+        <v>381.176470588235</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -417,48 +389,76 @@
       <c r="M7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="1"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="0" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <f aca="false">(C7*D7/60)*F8</f>
-        <v>14</v>
-      </c>
-      <c r="H8" s="3" t="n">
+        <f aca="false">(C7*60/D7)*F8</f>
+        <v>14.8235294117647</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <f aca="false">G8*60</f>
-        <v>840</v>
+        <v>889.411764705882</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1000</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>500</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <f aca="false">C9*60/D9</f>
+        <v>18</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <f aca="false">G9*60</f>
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C10" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <f aca="false">C9*D9/60</f>
-        <v>16.6666666666667</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <f aca="false">G9*60</f>
-        <v>1000</v>
+      <c r="D10" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <f aca="false">C10*60/D10</f>
+        <v>50</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <f aca="false">G10*60</f>
+        <v>3000</v>
       </c>
     </row>
   </sheetData>
